--- a/structural_feature/dataset/test_origin.xlsx
+++ b/structural_feature/dataset/test_origin.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$4489</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2689,6 +2692,9 @@
   <sheetPr/>
   <dimension ref="A1:E4489"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="19.2727272727273" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -65540,6 +65546,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:E4489" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
